--- a/src/src/main/webapp/portal/asset/fileAttachment/zkbFileAttachment/Directory_Service_Template.xlsx
+++ b/src/src/main/webapp/portal/asset/fileAttachment/zkbFileAttachment/Directory_Service_Template.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="22527"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C9DBBBE-73CC-4080-8D9D-FD2F7BA48304}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B0A837C-F608-4737-A519-C30FD25D585F}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,22 +26,22 @@
     <t>填写说明</t>
   </si>
   <si>
-    <t>主目录</t>
-  </si>
-  <si>
-    <t>子目录</t>
-  </si>
-  <si>
     <t>1. SYSTEM_ID必须填写</t>
   </si>
   <si>
-    <t>2. 主目录必须填写</t>
-  </si>
-  <si>
-    <t>3. 子目录必须填写</t>
-  </si>
-  <si>
     <t>系统ID</t>
+  </si>
+  <si>
+    <t>Modality</t>
+  </si>
+  <si>
+    <t>Product</t>
+  </si>
+  <si>
+    <t>2. Modality必须填写</t>
+  </si>
+  <si>
+    <t>3. Product必须填写</t>
   </si>
 </sst>
 </file>
@@ -469,13 +469,13 @@
   <sheetData>
     <row r="1" spans="1:3" s="2" customFormat="1">
       <c r="A1" s="2" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -506,7 +506,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="5" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B2" s="6"/>
       <c r="C2" s="6"/>
@@ -517,7 +517,7 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3" s="5" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B3" s="6"/>
       <c r="C3" s="6"/>
@@ -528,7 +528,7 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4" s="5" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B4" s="6"/>
       <c r="C4" s="6"/>
